--- a/seed/PHPPS_Portfolio_Data.xlsx
+++ b/seed/PHPPS_Portfolio_Data.xlsx
@@ -3550,12 +3550,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Drawing animals</t>
+          <t>Helping my friends</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2027-01-15 15:05</t>
+          <t>2027-01-30 12:12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -3590,13 +3590,13 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Resilience</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2027-01-15 15:05</t>
+          <t>2027-01-30 12:12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2027-01-15 15:05</t>
+          <t>2027-01-30 12:12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3673,12 +3673,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I want to learn my multiplication tables up to 12 by heart.</t>
+          <t>I want to finish my homework on time without being reminded.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2027-01-15 15:05</t>
+          <t>2027-01-30 12:12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2027-01-15 15:05</t>
+          <t>2027-01-30 12:12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3755,12 +3755,12 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Practise the piano every day</t>
+          <t>Join the school football team</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2027-01-15 15:05</t>
+          <t>2027-01-30 12:12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3795,13 +3795,13 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2027-03-10 14:12</t>
+          <t>2027-03-12 16:20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3836,13 +3836,13 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brother or sister</t>
+          <t>Friend</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2027-03-10 14:12</t>
+          <t>2027-03-12 16:20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3876,10 +3876,14 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I miss my best friend who moved to another school.</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2027-03-10 14:12</t>
+          <t>2027-03-12 16:20</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3914,13 +3918,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2027-03-10 14:12</t>
+          <t>2027-03-12 16:20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3956,12 +3960,12 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Practising with past questions.</t>
+          <t>Using mind maps to revise.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2027-03-10 14:12</t>
+          <t>2027-03-12 16:20</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3997,12 +4001,12 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I tried again when I made mistakes in my spelling.</t>
+          <t>I invited a new classmate to play with us and now we are friends.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2027-03-10 14:12</t>
+          <t>2027-03-12 16:20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4038,12 +4042,12 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Solving puzzles</t>
+          <t>Swimming</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2027-01-14 13:20</t>
+          <t>2027-01-23 10:05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4078,13 +4082,13 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Integrity</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2027-01-14 13:20</t>
+          <t>2027-01-23 10:05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4120,12 +4124,12 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Drawing on my tablet</t>
+          <t>Practising silat</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2027-01-14 13:20</t>
+          <t>2027-01-23 10:05</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4161,12 +4165,12 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I want to learn my multiplication tables up to 12 by heart.</t>
+          <t>I want to improve my problem sums in Mathematics by checking my working.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2027-01-14 13:20</t>
+          <t>2027-01-23 10:05</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4202,12 +4206,12 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I want to be kinder to classmates. I will invite someone new to play at recess.</t>
+          <t>I want to be more responsible. I will pack my school bag every night.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2027-01-14 13:20</t>
+          <t>2027-01-23 10:05</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4243,12 +4247,12 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sleep before 10 pm</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2027-01-14 13:20</t>
+          <t>2027-01-23 10:05</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4283,13 +4287,13 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2027-03-13 11:12</t>
+          <t>2027-03-09 11:05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4330,7 +4334,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2027-03-13 11:12</t>
+          <t>2027-03-09 11:05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -4364,14 +4368,10 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>No, I am fine.</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2027-03-13 11:12</t>
+          <t>2027-03-09 11:05</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -4406,13 +4406,13 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2027-03-13 11:12</t>
+          <t>2027-03-09 11:05</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4448,12 +4448,12 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Watching the videos in class.</t>
+          <t>Practising with past questions.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2027-03-13 11:12</t>
+          <t>2027-03-09 11:05</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4489,12 +4489,12 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I put up my hand more often in Science.</t>
+          <t>I invited a new classmate to play with us and now we are friends.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2027-03-13 11:12</t>
+          <t>2027-03-09 11:05</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4530,12 +4530,12 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Remembering facts about space</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2027-01-17 15:20</t>
+          <t>2027-01-23 14:41</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -4570,13 +4570,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Responsibility</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2027-01-17 15:20</t>
+          <t>2027-01-23 14:41</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -4612,12 +4612,12 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dancing</t>
+          <t>Practising silat</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2027-01-17 15:20</t>
+          <t>2027-01-23 14:41</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4653,12 +4653,12 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I want to learn my multiplication tables up to 12 by heart.</t>
+          <t>I want to improve my problem sums in Mathematics by checking my working.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2027-01-17 15:20</t>
+          <t>2027-01-23 14:41</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4694,12 +4694,12 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I want to be more patient with my younger brother. I will count to five before I respond.</t>
+          <t>I want to show respect by listening without interrupting.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2027-01-17 15:20</t>
+          <t>2027-01-23 14:41</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2027-01-17 15:20</t>
+          <t>2027-01-23 14:41</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4781,7 +4781,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2027-03-10 08:20</t>
+          <t>2027-03-12 10:05</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4822,7 +4822,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2027-03-10 08:20</t>
+          <t>2027-03-12 10:05</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4859,7 +4859,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2027-03-10 08:20</t>
+          <t>2027-03-12 10:05</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4900,7 +4900,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2027-03-10 08:20</t>
+          <t>2027-03-12 10:05</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4936,12 +4936,12 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Watching the videos in class.</t>
+          <t>When my teacher showed us with real objects.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2027-03-10 08:20</t>
+          <t>2027-03-12 10:05</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4977,12 +4977,12 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I put up my hand more often in Science.</t>
+          <t>I invited a new classmate to play with us and now we are friends.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2027-03-10 08:20</t>
+          <t>2027-03-12 10:05</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5018,12 +5018,12 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Helping my friends</t>
+          <t>Swimming</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2027-01-30 09:12</t>
+          <t>2027-01-23 12:12</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5058,13 +5058,13 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Care</t>
+          <t>Responsibility</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2027-01-30 09:12</t>
+          <t>2027-01-23 12:12</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5100,12 +5100,12 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Baking cookies with my grandmother</t>
+          <t>Cycling at the park with my family</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2027-01-30 09:12</t>
+          <t>2027-01-23 12:12</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5141,12 +5141,12 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I want to improve my problem sums in Mathematics by checking my working.</t>
+          <t>I want to speak more confidently in Mother Tongue oral.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2027-01-30 09:12</t>
+          <t>2027-01-23 12:12</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5182,12 +5182,12 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I want to be more resilient. When I get something wrong, I will try again instead of giving up.</t>
+          <t>I want to be more patient with my younger brother. I will count to five before I respond.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2027-01-30 09:12</t>
+          <t>2027-01-23 12:12</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2027-01-30 09:12</t>
+          <t>2027-01-23 12:12</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5269,7 +5269,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2027-03-13 16:34</t>
+          <t>2027-03-09 13:34</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5304,13 +5304,13 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Parent or guardian</t>
+          <t>Brother or sister</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2027-03-13 16:34</t>
+          <t>2027-03-09 13:34</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2027-03-13 16:34</t>
+          <t>2027-03-09 13:34</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5386,13 +5386,13 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2027-03-13 16:34</t>
+          <t>2027-03-09 13:34</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5428,12 +5428,12 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Doing group work with my friends.</t>
+          <t>When my teacher showed us with real objects.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2027-03-13 16:34</t>
+          <t>2027-03-09 13:34</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5469,12 +5469,12 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I packed my bag every night except twice.</t>
+          <t>I invited a new classmate to play with us and now we are friends.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2027-03-13 16:34</t>
+          <t>2027-03-09 13:34</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5510,12 +5510,12 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Writing stories</t>
+          <t>Helping my friends</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2027-01-13 09:20</t>
+          <t>2027-01-18 10:12</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5550,13 +5550,13 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Resilience</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2027-01-13 09:20</t>
+          <t>2027-01-18 10:12</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2027-01-13 09:20</t>
+          <t>2027-01-18 10:12</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5633,12 +5633,12 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I want to finish my homework on time without being reminded.</t>
+          <t>I want to write longer compositions with better vocabulary.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2027-01-13 09:20</t>
+          <t>2027-01-18 10:12</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2027-01-13 09:20</t>
+          <t>2027-01-18 10:12</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5715,12 +5715,12 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Learn to cook fried rice</t>
+          <t>Sleep before 10 pm</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2027-01-13 09:20</t>
+          <t>2027-01-18 10:12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5761,7 +5761,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2027-03-09 09:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5796,13 +5796,13 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Form teacher</t>
+          <t>Parent or guardian</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2027-03-09 09:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5838,12 +5838,12 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I miss my best friend who moved to another school.</t>
+          <t>Nothing for now.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2027-03-09 09:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5884,7 +5884,7 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2027-03-09 09:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5920,12 +5920,12 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Doing group work with my friends.</t>
+          <t>When I asked questions after class.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2027-03-09 09:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5961,12 +5961,12 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I counted to five most of the time, but sometimes I forgot.</t>
+          <t>I invited a new classmate to play with us and now we are friends.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2027-03-09 09:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6002,12 +6002,12 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Playing the piano</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2027-01-12 13:58</t>
+          <t>2027-01-20 15:20</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6042,13 +6042,13 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Care</t>
+          <t>Responsibility</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2027-01-12 13:58</t>
+          <t>2027-01-20 15:20</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6084,12 +6084,12 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Visiting the library</t>
+          <t>Playing badminton</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2027-01-12 13:58</t>
+          <t>2027-01-20 15:20</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2027-01-12 13:58</t>
+          <t>2027-01-20 15:20</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6166,12 +6166,12 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I want to be braver. I will put up my hand to answer at least once a day.</t>
+          <t>I want to show respect by listening without interrupting.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2027-01-12 13:58</t>
+          <t>2027-01-20 15:20</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6207,12 +6207,12 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Join the school football team</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2027-01-12 13:58</t>
+          <t>2027-01-20 15:20</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6253,7 +6253,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2027-03-12 15:12</t>
+          <t>2027-03-09 08:58</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6288,13 +6288,13 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Brother or sister</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2027-03-12 15:12</t>
+          <t>2027-03-09 08:58</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6331,7 +6331,7 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2027-03-12 15:12</t>
+          <t>2027-03-09 08:58</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6366,13 +6366,13 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2027-03-12 15:12</t>
+          <t>2027-03-09 08:58</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6408,12 +6408,12 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Practising with past questions.</t>
+          <t>Watching the videos in class.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2027-03-12 15:12</t>
+          <t>2027-03-09 08:58</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6449,12 +6449,12 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I packed my bag every night except twice.</t>
+          <t>I counted to five most of the time, but sometimes I forgot.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2027-03-12 15:12</t>
+          <t>2027-03-09 08:58</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6490,12 +6490,12 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Helping my friends</t>
+          <t>Reading story books</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2027-01-12 15:58</t>
+          <t>2027-01-22 12:41</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6530,13 +6530,13 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Respect</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2027-01-12 15:58</t>
+          <t>2027-01-22 12:41</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2027-01-12 15:58</t>
+          <t>2027-01-22 12:41</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2027-01-12 15:58</t>
+          <t>2027-01-22 12:41</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6654,12 +6654,12 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I want to show respect by listening without interrupting.</t>
+          <t>I want to be more resilient. When I get something wrong, I will try again instead of giving up.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2027-01-12 15:58</t>
+          <t>2027-01-22 12:41</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2027-01-12 15:58</t>
+          <t>2027-01-22 12:41</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6735,13 +6735,13 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2027-03-10 13:58</t>
+          <t>2027-03-13 10:05</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6776,13 +6776,13 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Parent or guardian</t>
+          <t>Friend</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2027-03-10 13:58</t>
+          <t>2027-03-13 10:05</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6819,7 +6819,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2027-03-10 13:58</t>
+          <t>2027-03-13 10:05</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6854,13 +6854,13 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2027-03-10 13:58</t>
+          <t>2027-03-13 10:05</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6896,12 +6896,12 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Watching the videos in class.</t>
+          <t>Doing group work with my friends.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2027-03-10 13:58</t>
+          <t>2027-03-13 10:05</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6937,12 +6937,12 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I put up my hand more often in Science.</t>
+          <t>I tried again when I made mistakes in my spelling.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2027-03-10 13:58</t>
+          <t>2027-03-13 10:05</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6978,12 +6978,12 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Remembering facts about space</t>
+          <t>Helping my friends</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2027-01-16 12:34</t>
+          <t>2027-01-13 16:20</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7018,13 +7018,13 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Responsibility</t>
+          <t>Integrity</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2027-01-16 12:34</t>
+          <t>2027-01-13 16:20</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2027-01-16 12:34</t>
+          <t>2027-01-13 16:20</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7101,12 +7101,12 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I want to finish my homework on time without being reminded.</t>
+          <t>I want to write longer compositions with better vocabulary.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2027-01-16 12:34</t>
+          <t>2027-01-13 16:20</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7142,12 +7142,12 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I want to show respect by listening without interrupting.</t>
+          <t>I want to be kinder to classmates. I will invite someone new to play at recess.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2027-01-16 12:34</t>
+          <t>2027-01-13 16:20</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7183,12 +7183,12 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sleep before 10 pm</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2027-01-16 12:34</t>
+          <t>2027-01-13 16:20</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7223,13 +7223,13 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2027-03-11 13:12</t>
+          <t>2027-03-12 15:58</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -7264,13 +7264,13 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brother or sister</t>
+          <t>Friend</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2027-03-11 13:12</t>
+          <t>2027-03-12 15:58</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -7304,14 +7304,10 @@
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>I am nervous about the swimming test.</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2027-03-11 13:12</t>
+          <t>2027-03-12 15:58</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7346,13 +7342,13 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2027-03-11 13:12</t>
+          <t>2027-03-12 15:58</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7388,12 +7384,12 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>When I asked questions after class.</t>
+          <t>Watching the videos in class.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2027-03-11 13:12</t>
+          <t>2027-03-12 15:58</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7429,12 +7425,12 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I counted to five most of the time, but sometimes I forgot.</t>
+          <t>I packed my bag every night except twice.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2027-03-11 13:12</t>
+          <t>2027-03-12 15:58</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7470,12 +7466,12 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Telling jokes</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2027-01-18 15:12</t>
+          <t>2027-01-15 11:34</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7516,7 +7512,7 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2027-01-18 15:12</t>
+          <t>2027-01-15 11:34</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7552,12 +7548,12 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Playing badminton</t>
+          <t>Going to the beach</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2027-01-18 15:12</t>
+          <t>2027-01-15 11:34</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7593,12 +7589,12 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I want to read one English story book every week.</t>
+          <t>I want to explain Science answers using the right keywords.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2027-01-18 15:12</t>
+          <t>2027-01-15 11:34</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7634,12 +7630,12 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I want to be braver. I will put up my hand to answer at least once a day.</t>
+          <t>I want to show respect by listening without interrupting.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2027-01-18 15:12</t>
+          <t>2027-01-15 11:34</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7675,12 +7671,12 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Learn to cook fried rice</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2027-01-18 15:12</t>
+          <t>2027-01-15 11:34</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7715,13 +7711,13 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2027-03-11 11:20</t>
+          <t>2027-03-12 10:12</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7756,13 +7752,13 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Brother or sister</t>
+          <t>Friend</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2027-03-11 11:20</t>
+          <t>2027-03-12 10:12</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7798,12 +7794,12 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>No, I am fine.</t>
+          <t>I miss my best friend who moved to another school.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2027-03-11 11:20</t>
+          <t>2027-03-12 10:12</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7838,13 +7834,13 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2027-03-11 11:20</t>
+          <t>2027-03-12 10:12</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7880,12 +7876,12 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Watching the videos in class.</t>
+          <t>Doing group work with my friends.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2027-03-11 11:20</t>
+          <t>2027-03-12 10:12</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7921,12 +7917,12 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I invited Kai Xuan to play with us and now we are friends.</t>
+          <t>I put up my hand more often in Science.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2027-03-11 11:20</t>
+          <t>2027-03-12 10:12</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7962,12 +7958,12 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Solving puzzles</t>
+          <t>Running fast</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2027-01-21 12:12</t>
+          <t>2027-01-22 11:20</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8002,13 +7998,13 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Respect</t>
+          <t>Integrity</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2027-01-21 12:12</t>
+          <t>2027-01-22 11:20</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8044,12 +8040,12 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Reading comics</t>
+          <t>Taking care of my fish</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2027-01-21 12:12</t>
+          <t>2027-01-22 11:20</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8085,12 +8081,12 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I want to explain Science answers using the right keywords.</t>
+          <t>I want to learn my multiplication tables up to 12 by heart.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2027-01-21 12:12</t>
+          <t>2027-01-22 11:20</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8131,7 +8127,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2027-01-21 12:12</t>
+          <t>2027-01-22 11:20</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8172,7 +8168,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2027-01-21 12:12</t>
+          <t>2027-01-22 11:20</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8207,13 +8203,13 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2027-03-09 15:05</t>
+          <t>2027-03-12 13:12</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8254,7 +8250,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2027-03-09 15:05</t>
+          <t>2027-03-12 13:12</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8290,12 +8286,12 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I am nervous about the swimming test.</t>
+          <t>I miss my best friend who moved to another school.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2027-03-09 15:05</t>
+          <t>2027-03-12 13:12</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8330,13 +8326,13 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2027-03-09 15:05</t>
+          <t>2027-03-12 13:12</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8372,12 +8368,12 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>When I asked questions after class.</t>
+          <t>When my teacher showed us with real objects.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2027-03-09 15:05</t>
+          <t>2027-03-12 13:12</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8413,12 +8409,12 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I packed my bag every night except twice.</t>
+          <t>I tried again when I made mistakes in my spelling.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2027-03-09 15:05</t>
+          <t>2027-03-12 13:12</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8454,12 +8450,12 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Building with Lego</t>
+          <t>Remembering facts about space</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2027-01-21 12:41</t>
+          <t>2027-01-27 11:41</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8494,13 +8490,13 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Respect</t>
+          <t>Harmony</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2027-01-21 12:41</t>
+          <t>2027-01-27 11:41</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8536,12 +8532,12 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Drawing on my tablet</t>
+          <t>Baking cookies with my grandmother</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2027-01-21 12:41</t>
+          <t>2027-01-27 11:41</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8577,12 +8573,12 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I want to improve my problem sums in Mathematics by checking my working.</t>
+          <t>I want to explain Science answers using the right keywords.</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2027-01-21 12:41</t>
+          <t>2027-01-27 11:41</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8618,12 +8614,12 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I want to show respect by listening without interrupting.</t>
+          <t>I want to be kinder to classmates. I will invite someone new to play at recess.</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2027-01-21 12:41</t>
+          <t>2027-01-27 11:41</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8659,12 +8655,12 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Sleep before 10 pm</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2027-01-21 12:41</t>
+          <t>2027-01-27 11:41</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8699,13 +8695,13 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2027-03-11 09:12</t>
+          <t>2027-03-10 09:34</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8740,13 +8736,13 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brother or sister</t>
+          <t>Parent or guardian</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2027-03-11 09:12</t>
+          <t>2027-03-10 09:34</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8780,14 +8776,10 @@
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Nothing for now.</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2027-03-11 09:12</t>
+          <t>2027-03-10 09:34</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8822,13 +8814,13 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2027-03-11 09:12</t>
+          <t>2027-03-10 09:34</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8864,12 +8856,12 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Doing group work with my friends.</t>
+          <t>Using mind maps to revise.</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2027-03-11 09:12</t>
+          <t>2027-03-10 09:34</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8905,12 +8897,12 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>I packed my bag every night except twice.</t>
+          <t>I tried to listen more. My teacher noticed it.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2027-03-11 09:12</t>
+          <t>2027-03-10 09:34</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8946,12 +8938,12 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Playing the piano</t>
+          <t>Solving puzzles</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2027-01-14 10:58</t>
+          <t>2027-01-15 10:20</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8986,13 +8978,13 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Integrity</t>
+          <t>Care</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2027-01-14 10:58</t>
+          <t>2027-01-15 10:20</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9028,12 +9020,12 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Watching nature documentaries</t>
+          <t>Reading comics</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2027-01-14 10:58</t>
+          <t>2027-01-15 10:20</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9069,12 +9061,12 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>I want to finish my homework on time without being reminded.</t>
+          <t>I want to read one English story book every week.</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2027-01-14 10:58</t>
+          <t>2027-01-15 10:20</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9110,12 +9102,12 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I want to be more responsible. I will pack my school bag every night.</t>
+          <t>I want to be braver. I will put up my hand to answer at least once a day.</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2027-01-14 10:58</t>
+          <t>2027-01-15 10:20</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9151,12 +9143,12 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Practise the piano every day</t>
+          <t>Learn to swim 50 metres</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2027-01-14 10:58</t>
+          <t>2027-01-15 10:20</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9197,7 +9189,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2027-03-09 10:05</t>
+          <t>2027-03-11 14:12</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9232,13 +9224,13 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Brother or sister</t>
+          <t>Form teacher</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2027-03-09 10:05</t>
+          <t>2027-03-11 14:12</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9279,7 +9271,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2027-03-09 10:05</t>
+          <t>2027-03-11 14:12</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9314,13 +9306,13 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2027-03-09 10:05</t>
+          <t>2027-03-11 14:12</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9356,12 +9348,12 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Using mind maps to revise.</t>
+          <t>Doing group work with my friends.</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2027-03-09 10:05</t>
+          <t>2027-03-11 14:12</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9402,7 +9394,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2027-03-09 10:05</t>
+          <t>2027-03-11 14:12</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9438,12 +9430,12 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Helping my friends</t>
+          <t>Solving puzzles</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2027-01-22 11:12</t>
+          <t>2027-01-13 13:05</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9478,13 +9470,13 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Respect</t>
+          <t>Resilience</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2027-01-22 11:12</t>
+          <t>2027-01-13 13:05</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9525,7 +9517,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2027-01-22 11:12</t>
+          <t>2027-01-13 13:05</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9566,7 +9558,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2027-01-22 11:12</t>
+          <t>2027-01-13 13:05</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9602,12 +9594,12 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>I want to be more responsible. I will pack my school bag every night.</t>
+          <t>I want to show respect by listening without interrupting.</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2027-01-22 11:12</t>
+          <t>2027-01-13 13:05</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9643,12 +9635,12 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Practise the piano every day</t>
+          <t>Join the school football team</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2027-01-22 11:12</t>
+          <t>2027-01-13 13:05</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9683,13 +9675,13 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2027-03-10 09:20</t>
+          <t>2027-03-11 13:20</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9724,13 +9716,13 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Parent or guardian</t>
+          <t>Form teacher</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2027-03-10 09:20</t>
+          <t>2027-03-11 13:20</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9767,7 +9759,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2027-03-10 09:20</t>
+          <t>2027-03-11 13:20</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9802,13 +9794,13 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2027-03-10 09:20</t>
+          <t>2027-03-11 13:20</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9844,12 +9836,12 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>When I asked questions after class.</t>
+          <t>Doing group work with my friends.</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2027-03-10 09:20</t>
+          <t>2027-03-11 13:20</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9885,12 +9877,12 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I packed my bag every night except twice.</t>
+          <t>I put up my hand more often in Science.</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2027-03-10 09:20</t>
+          <t>2027-03-11 13:20</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9926,12 +9918,12 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Solving puzzles</t>
+          <t>Playing the piano</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2027-01-28 10:34</t>
+          <t>2027-01-17 11:41</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9966,13 +9958,13 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Integrity</t>
+          <t>Responsibility</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2027-01-28 10:34</t>
+          <t>2027-01-17 11:41</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10013,7 +10005,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2027-01-28 10:34</t>
+          <t>2027-01-17 11:41</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10049,12 +10041,12 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I want to learn my multiplication tables up to 12 by heart.</t>
+          <t>I want to explain Science answers using the right keywords.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2027-01-28 10:34</t>
+          <t>2027-01-17 11:41</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10090,12 +10082,12 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>I want to show respect by listening without interrupting.</t>
+          <t>I want to be more patient with my younger brother. I will count to five before I respond.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2027-01-28 10:34</t>
+          <t>2027-01-17 11:41</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10131,12 +10123,12 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Practise the piano every day</t>
+          <t>Read 30 books this year</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2027-01-28 10:34</t>
+          <t>2027-01-17 11:41</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10171,13 +10163,13 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2027-03-13 08:34</t>
+          <t>2027-03-10 12:12</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10218,7 +10210,7 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2027-03-13 08:34</t>
+          <t>2027-03-10 12:12</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10254,12 +10246,12 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I miss my best friend who moved to another school.</t>
+          <t>Nothing for now.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2027-03-13 08:34</t>
+          <t>2027-03-10 12:12</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10294,13 +10286,13 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2027-03-13 08:34</t>
+          <t>2027-03-10 12:12</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10341,7 +10333,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2027-03-13 08:34</t>
+          <t>2027-03-10 12:12</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10377,12 +10369,12 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I tried again when I made mistakes in my spelling.</t>
+          <t>I counted to five most of the time, but sometimes I forgot.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2027-03-13 08:34</t>
+          <t>2027-03-10 12:12</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10418,12 +10410,12 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Writing stories</t>
+          <t>Playing the piano</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2027-01-14 11:58</t>
+          <t>2027-01-26 12:20</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10458,13 +10450,13 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Integrity</t>
         </is>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2027-01-14 11:58</t>
+          <t>2027-01-26 12:20</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10500,12 +10492,12 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Visiting the library</t>
+          <t>Dancing</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2027-01-14 11:58</t>
+          <t>2027-01-26 12:20</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10541,12 +10533,12 @@
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I want to speak more confidently in Mother Tongue oral.</t>
+          <t>I want to read one English story book every week.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2027-01-14 11:58</t>
+          <t>2027-01-26 12:20</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -10582,12 +10574,12 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I want to be more patient with my younger brother. I will count to five before I respond.</t>
+          <t>I want to be more resilient. When I get something wrong, I will try again instead of giving up.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2027-01-14 11:58</t>
+          <t>2027-01-26 12:20</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10623,12 +10615,12 @@
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Read 30 books this year</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2027-01-14 11:58</t>
+          <t>2027-01-26 12:20</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10663,13 +10655,13 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2027-03-10 15:05</t>
+          <t>2027-03-12 11:34</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10704,13 +10696,13 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Form teacher</t>
         </is>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2027-03-10 15:05</t>
+          <t>2027-03-12 11:34</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10744,14 +10736,10 @@
         </is>
       </c>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>I am a bit worried about my Mathematics test.</t>
-        </is>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2027-03-10 15:05</t>
+          <t>2027-03-12 11:34</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10786,13 +10774,13 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2027-03-10 15:05</t>
+          <t>2027-03-12 11:34</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10833,7 +10821,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2027-03-10 15:05</t>
+          <t>2027-03-12 11:34</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10869,12 +10857,12 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I tried again when I made mistakes in my spelling.</t>
+          <t>I invited a new classmate to play with us and now we are friends.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2027-03-10 15:05</t>
+          <t>2027-03-12 11:34</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -10910,12 +10898,12 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Running fast</t>
+          <t>Remembering facts about space</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2027-01-18 14:58</t>
+          <t>2027-01-26 08:05</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -10950,13 +10938,13 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Care</t>
+          <t>Integrity</t>
         </is>
       </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2027-01-18 14:58</t>
+          <t>2027-01-26 08:05</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -10992,12 +10980,12 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dancing</t>
+          <t>Going to the beach</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2027-01-18 14:58</t>
+          <t>2027-01-26 08:05</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11033,12 +11021,12 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I want to read one English story book every week.</t>
+          <t>I want to learn my multiplication tables up to 12 by heart.</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2027-01-18 14:58</t>
+          <t>2027-01-26 08:05</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11074,12 +11062,12 @@
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I want to be kinder to classmates. I will invite someone new to play at recess.</t>
+          <t>I want to be braver. I will put up my hand to answer at least once a day.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2027-01-18 14:58</t>
+          <t>2027-01-26 08:05</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11115,12 +11103,12 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Learn to swim 50 metres</t>
+          <t>Read 30 books this year</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2027-01-18 14:58</t>
+          <t>2027-01-26 08:05</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11155,13 +11143,13 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2027-03-11 08:34</t>
+          <t>2027-03-12 13:34</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11196,13 +11184,13 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Brother or sister</t>
+          <t>Parent or guardian</t>
         </is>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2027-03-11 08:34</t>
+          <t>2027-03-12 13:34</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11243,7 +11231,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2027-03-11 08:34</t>
+          <t>2027-03-12 13:34</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -11278,13 +11266,13 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2027-03-11 08:34</t>
+          <t>2027-03-12 13:34</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -11320,12 +11308,12 @@
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Watching the videos in class.</t>
+          <t>When my teacher showed us with real objects.</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2027-03-11 08:34</t>
+          <t>2027-03-12 13:34</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11361,12 +11349,12 @@
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I tried again when I made mistakes in my spelling.</t>
+          <t>I put up my hand more often in Science.</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2027-03-11 08:34</t>
+          <t>2027-03-12 13:34</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11402,12 +11390,12 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Running fast</t>
+          <t>Solving puzzles</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2027-01-27 12:12</t>
+          <t>2027-01-23 08:58</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11442,13 +11430,13 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Responsibility</t>
+          <t>Care</t>
         </is>
       </c>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2027-01-27 12:12</t>
+          <t>2027-01-23 08:58</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -11484,12 +11472,12 @@
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Drawing on my tablet</t>
+          <t>Taking care of my fish</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2027-01-27 12:12</t>
+          <t>2027-01-23 08:58</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -11530,7 +11518,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2027-01-27 12:12</t>
+          <t>2027-01-23 08:58</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -11566,12 +11554,12 @@
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I want to be more resilient. When I get something wrong, I will try again instead of giving up.</t>
+          <t>I want to show respect by listening without interrupting.</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2027-01-27 12:12</t>
+          <t>2027-01-23 08:58</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -11607,12 +11595,12 @@
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Learn to swim 50 metres</t>
+          <t>Sleep before 10 pm</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2027-01-27 12:12</t>
+          <t>2027-01-23 08:58</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -11653,7 +11641,7 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2027-03-09 08:12</t>
+          <t>2027-03-12 08:05</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -11688,13 +11676,13 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Brother or sister</t>
+          <t>Parent or guardian</t>
         </is>
       </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2027-03-09 08:12</t>
+          <t>2027-03-12 08:05</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -11731,7 +11719,7 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2027-03-09 08:12</t>
+          <t>2027-03-12 08:05</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -11766,13 +11754,13 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2027-03-09 08:12</t>
+          <t>2027-03-12 08:05</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -11808,12 +11796,12 @@
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Doing group work with my friends.</t>
+          <t>Using mind maps to revise.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2027-03-09 08:12</t>
+          <t>2027-03-12 08:05</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -11849,12 +11837,12 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I invited Kai Xuan to play with us and now we are friends.</t>
+          <t>I packed my bag every night except twice.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2027-03-09 08:12</t>
+          <t>2027-03-12 08:05</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -11890,12 +11878,12 @@
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Swimming</t>
+          <t>Helping my friends</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2027-01-27 10:58</t>
+          <t>2027-01-26 16:12</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -11930,13 +11918,13 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Resilience</t>
+          <t>Harmony</t>
         </is>
       </c>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2027-01-27 10:58</t>
+          <t>2027-01-26 16:12</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -11972,12 +11960,12 @@
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Going to the beach</t>
+          <t>Cycling at the park with my family</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2027-01-27 10:58</t>
+          <t>2027-01-26 16:12</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -12013,12 +12001,12 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I want to speak more confidently in Mother Tongue oral.</t>
+          <t>I want to finish my homework on time without being reminded.</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2027-01-27 10:58</t>
+          <t>2027-01-26 16:12</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -12054,12 +12042,12 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I want to be more responsible. I will pack my school bag every night.</t>
+          <t>I want to be more patient with my younger brother. I will count to five before I respond.</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2027-01-27 10:58</t>
+          <t>2027-01-26 16:12</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -12095,12 +12083,12 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Make two new friends</t>
+          <t>Practise the piano every day</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2027-01-27 10:58</t>
+          <t>2027-01-26 16:12</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -12135,13 +12123,13 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2027-03-10 12:58</t>
+          <t>2027-03-11 16:58</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -12176,13 +12164,13 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Form teacher</t>
+          <t>Parent or guardian</t>
         </is>
       </c>
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2027-03-10 12:58</t>
+          <t>2027-03-11 16:58</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -12216,10 +12204,14 @@
         </is>
       </c>
       <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>I am nervous about the swimming test.</t>
+        </is>
+      </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2027-03-10 12:58</t>
+          <t>2027-03-11 16:58</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -12254,13 +12246,13 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2027-03-10 12:58</t>
+          <t>2027-03-11 16:58</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -12301,7 +12293,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2027-03-10 12:58</t>
+          <t>2027-03-11 16:58</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -12337,12 +12329,12 @@
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I invited Kai Xuan to play with us and now we are friends.</t>
+          <t>I tried to listen more. My teacher noticed it.</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2027-03-10 12:58</t>
+          <t>2027-03-11 16:58</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -12378,12 +12370,12 @@
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Drawing animals</t>
+          <t>Building with Lego</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2027-01-26 15:34</t>
+          <t>2027-01-29 08:58</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -12424,7 +12416,7 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2027-01-26 15:34</t>
+          <t>2027-01-29 08:58</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -12460,12 +12452,12 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Going to the beach</t>
+          <t>Drawing on my tablet</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2027-01-26 15:34</t>
+          <t>2027-01-29 08:58</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -12501,12 +12493,12 @@
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I want to read one English story book every week.</t>
+          <t>I want to explain Science answers using the right keywords.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2027-01-26 15:34</t>
+          <t>2027-01-29 08:58</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -12542,12 +12534,12 @@
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I want to be braver. I will put up my hand to answer at least once a day.</t>
+          <t>I want to be kinder to classmates. I will invite someone new to play at recess.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2027-01-26 15:34</t>
+          <t>2027-01-29 08:58</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -12583,12 +12575,12 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Join the school football team</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2027-01-26 15:34</t>
+          <t>2027-01-29 08:58</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -12629,7 +12621,7 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-09 13:12</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -12670,7 +12662,7 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-09 13:12</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -12711,7 +12703,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-09 13:12</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -12752,7 +12744,7 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-09 13:12</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -12788,12 +12780,12 @@
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Using mind maps to revise.</t>
+          <t>Watching the videos in class.</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-09 13:12</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -12829,12 +12821,12 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I put up my hand more often in Science.</t>
+          <t>I tried to listen more. My teacher noticed it.</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-09 13:12</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -12870,12 +12862,12 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Helping my friends</t>
+          <t>Building with Lego</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2027-01-23 15:34</t>
+          <t>2027-01-13 11:12</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -12910,13 +12902,13 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Care</t>
         </is>
       </c>
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2027-01-23 15:34</t>
+          <t>2027-01-13 11:12</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -12952,12 +12944,12 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Taking care of my fish</t>
+          <t>Playing chess with my father</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2027-01-23 15:34</t>
+          <t>2027-01-13 11:12</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -12993,12 +12985,12 @@
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I want to explain Science answers using the right keywords.</t>
+          <t>I want to write longer compositions with better vocabulary.</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2027-01-23 15:34</t>
+          <t>2027-01-13 11:12</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -13034,12 +13026,12 @@
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I want to show respect by listening without interrupting.</t>
+          <t>I want to be more patient with my younger brother. I will count to five before I respond.</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2027-01-23 15:34</t>
+          <t>2027-01-13 11:12</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -13075,12 +13067,12 @@
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Learn to swim 50 metres</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2027-01-23 15:34</t>
+          <t>2027-01-13 11:12</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -13115,13 +13107,13 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2027-03-09 08:05</t>
+          <t>2027-03-11 14:20</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -13162,7 +13154,7 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2027-03-09 08:05</t>
+          <t>2027-03-11 14:20</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -13196,14 +13188,10 @@
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>I miss my best friend who moved to another school.</t>
-        </is>
-      </c>
+      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2027-03-09 08:05</t>
+          <t>2027-03-11 14:20</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -13238,13 +13226,13 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2027-03-09 08:05</t>
+          <t>2027-03-11 14:20</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -13280,12 +13268,12 @@
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Using mind maps to revise.</t>
+          <t>When my teacher showed us with real objects.</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2027-03-09 08:05</t>
+          <t>2027-03-11 14:20</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -13321,12 +13309,12 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I tried to listen more. My teacher noticed it.</t>
+          <t>I counted to five most of the time, but sometimes I forgot.</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2027-03-09 08:05</t>
+          <t>2027-03-11 14:20</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -13362,12 +13350,12 @@
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Writing stories</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2027-01-18 15:34</t>
+          <t>2027-01-18 11:41</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -13402,13 +13390,13 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Respect</t>
+          <t>Harmony</t>
         </is>
       </c>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2027-01-18 15:34</t>
+          <t>2027-01-18 11:41</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -13444,12 +13432,12 @@
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Baking cookies with my grandmother</t>
+          <t>Dancing</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2027-01-18 15:34</t>
+          <t>2027-01-18 11:41</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -13485,12 +13473,12 @@
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>I want to speak more confidently in Mother Tongue oral.</t>
+          <t>I want to finish my homework on time without being reminded.</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2027-01-18 15:34</t>
+          <t>2027-01-18 11:41</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -13526,12 +13514,12 @@
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I want to be more responsible. I will pack my school bag every night.</t>
+          <t>I want to be kinder to classmates. I will invite someone new to play at recess.</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2027-01-18 15:34</t>
+          <t>2027-01-18 11:41</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -13567,12 +13555,12 @@
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Make two new friends</t>
+          <t>Read 30 books this year</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2027-01-18 15:34</t>
+          <t>2027-01-18 11:41</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -13607,13 +13595,13 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2027-03-13 12:34</t>
+          <t>2027-03-09 14:05</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -13648,13 +13636,13 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Form teacher</t>
+          <t>Parent or guardian</t>
         </is>
       </c>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2027-03-13 12:34</t>
+          <t>2027-03-09 14:05</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -13695,7 +13683,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2027-03-13 12:34</t>
+          <t>2027-03-09 14:05</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -13730,13 +13718,13 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2027-03-13 12:34</t>
+          <t>2027-03-09 14:05</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -13777,7 +13765,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2027-03-13 12:34</t>
+          <t>2027-03-09 14:05</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -13813,12 +13801,12 @@
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>I tried to listen more. My teacher noticed it.</t>
+          <t>I packed my bag every night except twice.</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2027-03-13 12:34</t>
+          <t>2027-03-09 14:05</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -13854,12 +13842,12 @@
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Building with Lego</t>
+          <t>Swimming</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2027-01-29 14:20</t>
+          <t>2027-01-26 10:20</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -13894,13 +13882,13 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Integrity</t>
+          <t>Harmony</t>
         </is>
       </c>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2027-01-29 14:20</t>
+          <t>2027-01-26 10:20</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -13936,12 +13924,12 @@
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Going to the beach</t>
+          <t>Practising silat</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2027-01-29 14:20</t>
+          <t>2027-01-26 10:20</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -13977,12 +13965,12 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>I want to explain Science answers using the right keywords.</t>
+          <t>I want to finish my homework on time without being reminded.</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2027-01-29 14:20</t>
+          <t>2027-01-26 10:20</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -14018,12 +14006,12 @@
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>I want to be more patient with my younger brother. I will count to five before I respond.</t>
+          <t>I want to be more responsible. I will pack my school bag every night.</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2027-01-29 14:20</t>
+          <t>2027-01-26 10:20</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -14059,12 +14047,12 @@
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Read 30 books this year</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2027-01-29 14:20</t>
+          <t>2027-01-26 10:20</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -14099,13 +14087,13 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G260" t="inlineStr"/>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2027-03-12 13:58</t>
+          <t>2027-03-11 09:41</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -14140,13 +14128,13 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Parent or guardian</t>
+          <t>Form teacher</t>
         </is>
       </c>
       <c r="G261" t="inlineStr"/>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2027-03-12 13:58</t>
+          <t>2027-03-11 09:41</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -14180,14 +14168,10 @@
         </is>
       </c>
       <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Nothing for now.</t>
-        </is>
-      </c>
+      <c r="G262" t="inlineStr"/>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2027-03-12 13:58</t>
+          <t>2027-03-11 09:41</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -14222,13 +14206,13 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2027-03-12 13:58</t>
+          <t>2027-03-11 09:41</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -14264,12 +14248,12 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>When I asked questions after class.</t>
+          <t>Doing group work with my friends.</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2027-03-12 13:58</t>
+          <t>2027-03-11 09:41</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -14305,12 +14289,12 @@
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>I counted to five most of the time, but sometimes I forgot.</t>
+          <t>I invited a new classmate to play with us and now we are friends.</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2027-03-12 13:58</t>
+          <t>2027-03-11 09:41</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -14346,12 +14330,12 @@
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Drawing animals</t>
+          <t>Helping my friends</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2027-01-28 14:12</t>
+          <t>2027-01-19 16:12</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -14386,13 +14370,13 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Respect</t>
+          <t>Responsibility</t>
         </is>
       </c>
       <c r="G267" t="inlineStr"/>
       <c r="H267" t="inlineStr">
         <is>
-          <t>2027-01-28 14:12</t>
+          <t>2027-01-19 16:12</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -14428,12 +14412,12 @@
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Drawing on my tablet</t>
+          <t>Reading comics</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>2027-01-28 14:12</t>
+          <t>2027-01-19 16:12</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -14469,12 +14453,12 @@
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
-          <t>I want to improve my problem sums in Mathematics by checking my working.</t>
+          <t>I want to finish my homework on time without being reminded.</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2027-01-28 14:12</t>
+          <t>2027-01-19 16:12</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -14515,7 +14499,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>2027-01-28 14:12</t>
+          <t>2027-01-19 16:12</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -14551,12 +14535,12 @@
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Learn to cook fried rice</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>2027-01-28 14:12</t>
+          <t>2027-01-19 16:12</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -14591,13 +14575,13 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G272" t="inlineStr"/>
       <c r="H272" t="inlineStr">
         <is>
-          <t>2027-03-10 10:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -14632,13 +14616,13 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Parent or guardian</t>
         </is>
       </c>
       <c r="G273" t="inlineStr"/>
       <c r="H273" t="inlineStr">
         <is>
-          <t>2027-03-10 10:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -14675,7 +14659,7 @@
       <c r="G274" t="inlineStr"/>
       <c r="H274" t="inlineStr">
         <is>
-          <t>2027-03-10 10:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -14710,13 +14694,13 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G275" t="inlineStr"/>
       <c r="H275" t="inlineStr">
         <is>
-          <t>2027-03-10 10:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -14757,7 +14741,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2027-03-10 10:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -14793,12 +14777,12 @@
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I counted to five most of the time, but sometimes I forgot.</t>
+          <t>I invited a new classmate to play with us and now we are friends.</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>2027-03-10 10:41</t>
+          <t>2027-03-12 10:34</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -14834,12 +14818,12 @@
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Telling jokes</t>
+          <t>Playing the piano</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>2027-01-23 08:34</t>
+          <t>2027-01-21 16:34</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -14874,13 +14858,13 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Harmony</t>
+          <t>Integrity</t>
         </is>
       </c>
       <c r="G279" t="inlineStr"/>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2027-01-23 08:34</t>
+          <t>2027-01-21 16:34</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -14916,12 +14900,12 @@
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Cycling at the park with my family</t>
+          <t>Practising silat</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2027-01-23 08:34</t>
+          <t>2027-01-21 16:34</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -14957,12 +14941,12 @@
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I want to finish my homework on time without being reminded.</t>
+          <t>I want to learn my multiplication tables up to 12 by heart.</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2027-01-23 08:34</t>
+          <t>2027-01-21 16:34</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -14998,12 +14982,12 @@
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I want to be braver. I will put up my hand to answer at least once a day.</t>
+          <t>I want to be kinder to classmates. I will invite someone new to play at recess.</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2027-01-23 08:34</t>
+          <t>2027-01-21 16:34</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -15039,12 +15023,12 @@
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Read 30 books this year</t>
+          <t>Practise the piano every day</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2027-01-23 08:34</t>
+          <t>2027-01-21 16:34</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -15079,13 +15063,13 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G284" t="inlineStr"/>
       <c r="H284" t="inlineStr">
         <is>
-          <t>2027-03-11 15:20</t>
+          <t>2027-03-13 10:34</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -15120,13 +15104,13 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Parent or guardian</t>
         </is>
       </c>
       <c r="G285" t="inlineStr"/>
       <c r="H285" t="inlineStr">
         <is>
-          <t>2027-03-11 15:20</t>
+          <t>2027-03-13 10:34</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -15162,12 +15146,12 @@
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
-          <t>No, I am fine.</t>
+          <t>I am a bit worried about my Mathematics test.</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>2027-03-11 15:20</t>
+          <t>2027-03-13 10:34</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -15202,13 +15186,13 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G287" t="inlineStr"/>
       <c r="H287" t="inlineStr">
         <is>
-          <t>2027-03-11 15:20</t>
+          <t>2027-03-13 10:34</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -15244,12 +15228,12 @@
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Doing group work with my friends.</t>
+          <t>When I asked questions after class.</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>2027-03-11 15:20</t>
+          <t>2027-03-13 10:34</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -15285,12 +15269,12 @@
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr">
         <is>
-          <t>I tried to listen more. My teacher noticed it.</t>
+          <t>I tried again when I made mistakes in my spelling.</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>2027-03-11 15:20</t>
+          <t>2027-03-13 10:34</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -15326,12 +15310,12 @@
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Solving puzzles</t>
+          <t>Drawing animals</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>2027-01-29 14:58</t>
+          <t>2027-01-28 10:12</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -15366,13 +15350,13 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Respect</t>
+          <t>Integrity</t>
         </is>
       </c>
       <c r="G291" t="inlineStr"/>
       <c r="H291" t="inlineStr">
         <is>
-          <t>2027-01-29 14:58</t>
+          <t>2027-01-28 10:12</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -15408,12 +15392,12 @@
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Practising silat</t>
+          <t>Dancing</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2027-01-29 14:58</t>
+          <t>2027-01-28 10:12</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -15454,7 +15438,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2027-01-29 14:58</t>
+          <t>2027-01-28 10:12</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -15490,12 +15474,12 @@
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
-          <t>I want to show respect by listening without interrupting.</t>
+          <t>I want to be kinder to classmates. I will invite someone new to play at recess.</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2027-01-29 14:58</t>
+          <t>2027-01-28 10:12</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -15531,12 +15515,12 @@
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Sleep before 10 pm</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2027-01-29 14:58</t>
+          <t>2027-01-28 10:12</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -15571,13 +15555,13 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G296" t="inlineStr"/>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-10 11:41</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -15612,13 +15596,13 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Parent or guardian</t>
         </is>
       </c>
       <c r="G297" t="inlineStr"/>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-10 11:41</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -15654,12 +15638,12 @@
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
-          <t>I am nervous about the swimming test.</t>
+          <t>I am a bit worried about my Mathematics test.</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-10 11:41</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -15694,13 +15678,13 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G299" t="inlineStr"/>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-10 11:41</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -15736,12 +15720,12 @@
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Watching the videos in class.</t>
+          <t>Practising with past questions.</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-10 11:41</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -15777,12 +15761,12 @@
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
-          <t>I invited Kai Xuan to play with us and now we are friends.</t>
+          <t>I counted to five most of the time, but sometimes I forgot.</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2027-03-13 11:41</t>
+          <t>2027-03-10 11:41</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -15818,12 +15802,12 @@
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Drawing animals</t>
+          <t>Writing stories</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>2027-01-22 08:41</t>
+          <t>2027-01-17 15:20</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -15864,7 +15848,7 @@
       <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr">
         <is>
-          <t>2027-01-22 08:41</t>
+          <t>2027-01-17 15:20</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -15900,12 +15884,12 @@
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Playing badminton</t>
+          <t>Dancing</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>2027-01-22 08:41</t>
+          <t>2027-01-17 15:20</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -15941,12 +15925,12 @@
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="inlineStr">
         <is>
-          <t>I want to finish my homework on time without being reminded.</t>
+          <t>I want to write longer compositions with better vocabulary.</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>2027-01-22 08:41</t>
+          <t>2027-01-17 15:20</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -15982,12 +15966,12 @@
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I want to show respect by listening without interrupting.</t>
+          <t>I want to be braver. I will put up my hand to answer at least once a day.</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>2027-01-22 08:41</t>
+          <t>2027-01-17 15:20</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -16028,7 +16012,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>2027-01-22 08:41</t>
+          <t>2027-01-17 15:20</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -16064,12 +16048,12 @@
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Drawing animals</t>
+          <t>Running fast</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>2027-01-18 11:41</t>
+          <t>2027-01-12 13:05</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -16104,13 +16088,13 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Integrity</t>
+          <t>Respect</t>
         </is>
       </c>
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr">
         <is>
-          <t>2027-01-18 11:41</t>
+          <t>2027-01-12 13:05</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -16146,12 +16130,12 @@
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Drawing on my tablet</t>
+          <t>Dancing</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>2027-01-18 11:41</t>
+          <t>2027-01-12 13:05</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -16192,7 +16176,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>2027-01-18 11:41</t>
+          <t>2027-01-12 13:05</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -16228,12 +16212,12 @@
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I want to be braver. I will put up my hand to answer at least once a day.</t>
+          <t>I want to be more patient with my younger brother. I will count to five before I respond.</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>2027-01-18 11:41</t>
+          <t>2027-01-12 13:05</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -16269,12 +16253,12 @@
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Sleep before 10 pm</t>
+          <t>Make two new friends</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>2027-01-18 11:41</t>
+          <t>2027-01-12 13:05</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -16389,20 +16373,24 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>I will check my spelling before I hand in my work.</t>
+          <t>I will read for 20 minutes every night.</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J2" t="n">
         <v>30</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>I did better than my target because I practised a lot.</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -16435,7 +16423,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -16481,15 +16469,15 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>I will redo my wrong questions.</t>
+          <t>I will revise the keywords for each topic.</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J4" t="n">
         <v>20</v>
@@ -16531,24 +16519,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>I will practise writing ten words a day.</t>
+          <t>I will read one Mother Tongue story every week.</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J5" t="n">
         <v>30</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>I forgot some keywords. I will make flash cards.</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -16581,7 +16565,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -16589,7 +16573,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J6" t="n">
         <v>30</v>
@@ -16627,7 +16611,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -16635,7 +16619,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
         <v>25</v>
@@ -16673,15 +16657,15 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>I will use the CER method to answer open-ended questions.</t>
+          <t>I will revise the keywords for each topic.</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
         <v>20</v>
@@ -16719,24 +16703,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>I will practise writing ten words a day.</t>
+          <t>I will read one Mother Tongue story every week.</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J9" t="n">
         <v>30</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Reading every night helped me understand the questions.</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -16773,16 +16753,20 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>I will check my spelling before I hand in my work.</t>
+          <t>I will read for 20 minutes every night.</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
         <v>30</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Reading every night helped me understand the questions.</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -16815,7 +16799,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -16823,12 +16807,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
         <v>25</v>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>I forgot some keywords. I will make flash cards.</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -16861,24 +16849,20 @@
         </is>
       </c>
       <c r="G12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>I will use the CER method to answer open-ended questions.</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>18</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>I will use the CER method to answer open-ended questions.</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>20</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>I ran out of time. Next time I will skip difficult questions first.</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -16911,22 +16895,22 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>I will read one Mother Tongue story every week.</t>
+          <t>I will practise writing ten words a day.</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J13" t="n">
         <v>30</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Reading every night helped me understand the questions.</t>
+          <t>I did better than my target because I practised a lot.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -16961,22 +16945,22 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>I will read for 20 minutes every night.</t>
+          <t>I will learn five new words every week.</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
         <v>30</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>I ran out of time. Next time I will skip difficult questions first.</t>
+          <t>I did not reach my target because I was careless in the last section.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -17011,7 +16995,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -17019,16 +17003,12 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
         <v>25</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>I did not reach my target because I was careless in the last section.</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -17061,20 +17041,24 @@
         </is>
       </c>
       <c r="G16" t="n">
+        <v>17</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>I will use the CER method to answer open-ended questions.</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>16</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>I will use the CER method to answer open-ended questions.</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>19</v>
       </c>
       <c r="J16" t="n">
         <v>20</v>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>I forgot some keywords. I will make flash cards.</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -17107,7 +17091,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -17115,7 +17099,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
         <v>30</v>
@@ -17157,18 +17141,18 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>I will learn five new words every week.</t>
+          <t>I will read for 20 minutes every night.</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
         <v>30</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>I did not understand the question. I will read it twice next time.</t>
+          <t>I did better than my target because I practised a lot.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -17203,15 +17187,15 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>I will ask my teacher when I do not understand.</t>
+          <t>I will check my working step by step.</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
         <v>25</v>
@@ -17249,7 +17233,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -17257,7 +17241,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" t="n">
         <v>20</v>
@@ -17341,24 +17325,20 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>I will learn five new words every week.</t>
+          <t>I will read for 20 minutes every night.</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J22" t="n">
         <v>30</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>I did better than my target because I practised a lot.</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -17391,15 +17371,15 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>I will ask my teacher when I do not understand.</t>
+          <t>I will check my working step by step.</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
         <v>25</v>
@@ -17437,7 +17417,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -17445,16 +17425,12 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
         <v>20</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>I did not reach my target because I was careless in the last section.</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -17487,20 +17463,24 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
+          <t>I will practise writing ten words a day.</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
         <v>30</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>I ran out of time. Next time I will skip difficult questions first.</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -17533,22 +17513,22 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>I will check my spelling before I hand in my work.</t>
+          <t>I will learn five new words every week.</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J26" t="n">
         <v>30</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Reading every night helped me understand the questions.</t>
+          <t>I did better than my target because I practised a lot.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -17583,15 +17563,15 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>I will ask my teacher when I do not understand.</t>
+          <t>I will check my working step by step.</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
         <v>25</v>
@@ -17633,11 +17613,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>I will revise the keywords for each topic.</t>
+          <t>I will use the CER method to answer open-ended questions.</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
         <v>20</v>
@@ -17675,7 +17655,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -17683,7 +17663,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
         <v>30</v>
@@ -17729,7 +17709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
         <v>30</v>
@@ -17767,15 +17747,15 @@
         </is>
       </c>
       <c r="G31" t="n">
+        <v>17</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>I will check my working step by step.</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>18</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>I will check my working step by step.</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>13</v>
       </c>
       <c r="J31" t="n">
         <v>25</v>
@@ -17813,24 +17793,20 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>I will redo my wrong questions.</t>
+          <t>I will revise the keywords for each topic.</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J32" t="n">
         <v>20</v>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>I did better than my target because I practised a lot.</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -17863,20 +17839,24 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>I will practise writing ten words a day.</t>
+          <t>I will read one Mother Tongue story every week.</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J33" t="n">
         <v>30</v>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>I did not reach my target because I was careless in the last section.</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -17909,15 +17889,15 @@
         </is>
       </c>
       <c r="G34" t="n">
+        <v>24</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>I will check my spelling before I hand in my work.</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>21</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>I will check my spelling before I hand in my work.</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>30</v>
       </c>
       <c r="J34" t="n">
         <v>30</v>
@@ -17955,24 +17935,20 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>I will practise ten problem sums every weekend.</t>
+          <t>I will ask my teacher when I do not understand.</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J35" t="n">
         <v>25</v>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>I ran out of time. Next time I will skip difficult questions first.</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -18005,24 +17981,20 @@
         </is>
       </c>
       <c r="G36" t="n">
+        <v>16</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>I will use the CER method to answer open-ended questions.</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>17</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>I will revise the keywords for each topic.</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>15</v>
       </c>
       <c r="J36" t="n">
         <v>20</v>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>I forgot some keywords. I will make flash cards.</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -18059,20 +18031,16 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
+          <t>I will read one Mother Tongue story every week.</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
         <v>30</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>I forgot some keywords. I will make flash cards.</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -18105,20 +18073,24 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>I will check my spelling before I hand in my work.</t>
+          <t>I will learn five new words every week.</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
         <v>30</v>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>I forgot some keywords. I will make flash cards.</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -18151,7 +18123,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -18159,12 +18131,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
         <v>25</v>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>I did better than my target because I practised a lot.</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -18197,15 +18173,15 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>I will use the CER method to answer open-ended questions.</t>
+          <t>I will redo my wrong questions.</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J40" t="n">
         <v>20</v>
@@ -18243,15 +18219,15 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>I will read one Mother Tongue story every week.</t>
+          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
         <v>30</v>
@@ -18289,15 +18265,15 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>I will read for 20 minutes every night.</t>
+          <t>I will learn five new words every week.</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
         <v>30</v>
@@ -18335,15 +18311,15 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>I will ask my teacher when I do not understand.</t>
+          <t>I will practise ten problem sums every weekend.</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
         <v>25</v>
@@ -18381,24 +18357,20 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>I will redo my wrong questions.</t>
+          <t>I will revise the keywords for each topic.</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J44" t="n">
         <v>20</v>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Reading every night helped me understand the questions.</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
@@ -18431,24 +18403,20 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>I will practise writing ten words a day.</t>
+          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
         <v>30</v>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>I ran out of time. Next time I will skip difficult questions first.</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -18481,20 +18449,24 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>I will check my spelling before I hand in my work.</t>
+          <t>I will learn five new words every week.</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
         <v>30</v>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>I forgot some keywords. I will make flash cards.</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -18527,24 +18499,20 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>I will ask my teacher when I do not understand.</t>
+          <t>I will check my working step by step.</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
         <v>25</v>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>I did not understand the question. I will read it twice next time.</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -18577,20 +18545,24 @@
         </is>
       </c>
       <c r="G48" t="n">
+        <v>18</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>I will use the CER method to answer open-ended questions.</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
         <v>15</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>I will redo my wrong questions.</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>18</v>
       </c>
       <c r="J48" t="n">
         <v>20</v>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>I ran out of time. Next time I will skip difficult questions first.</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -18623,15 +18595,15 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
+          <t>I will practise writing ten words a day.</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
         <v>30</v>
@@ -18669,24 +18641,20 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>I will read for 20 minutes every night.</t>
+          <t>I will learn five new words every week.</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
         <v>30</v>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>I forgot some keywords. I will make flash cards.</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -18719,20 +18687,24 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>I will ask my teacher when I do not understand.</t>
+          <t>I will practise ten problem sums every weekend.</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
         <v>25</v>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>I did better than my target because I practised a lot.</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -18765,7 +18737,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -18773,7 +18745,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
         <v>20</v>
@@ -18811,15 +18783,15 @@
         </is>
       </c>
       <c r="G53" t="n">
+        <v>25</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>I will read one Mother Tongue story every week.</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
         <v>23</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>24</v>
       </c>
       <c r="J53" t="n">
         <v>30</v>
@@ -18857,24 +18829,20 @@
         </is>
       </c>
       <c r="G54" t="n">
+        <v>25</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>I will learn five new words every week.</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
         <v>22</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>I will learn five new words every week.</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>27</v>
       </c>
       <c r="J54" t="n">
         <v>30</v>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>I did better than my target because I practised a lot.</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -18907,7 +18875,7 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -18961,7 +18929,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J56" t="n">
         <v>20</v>
@@ -19007,7 +18975,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
         <v>30</v>
@@ -19045,7 +19013,7 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -19058,11 +19026,7 @@
       <c r="J58" t="n">
         <v>30</v>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>I did better than my target because I practised a lot.</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -19095,20 +19059,24 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>I will practise ten problem sums every weekend.</t>
+          <t>I will ask my teacher when I do not understand.</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
         <v>25</v>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Reading every night helped me understand the questions.</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -19141,20 +19109,24 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>I will redo my wrong questions.</t>
+          <t>I will use the CER method to answer open-ended questions.</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J60" t="n">
         <v>20</v>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>I did not understand the question. I will read it twice next time.</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -19187,15 +19159,15 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>I will read one Mother Tongue story every week.</t>
+          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
         <v>30</v>
@@ -19233,15 +19205,15 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>I will read for 20 minutes every night.</t>
+          <t>I will check my spelling before I hand in my work.</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
         <v>30</v>
@@ -19279,20 +19251,24 @@
         </is>
       </c>
       <c r="G63" t="n">
+        <v>18</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>I will ask my teacher when I do not understand.</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
         <v>17</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>I will ask my teacher when I do not understand.</t>
-        </is>
-      </c>
-      <c r="I63" t="n">
-        <v>25</v>
       </c>
       <c r="J63" t="n">
         <v>25</v>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>I forgot some keywords. I will make flash cards.</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -19325,20 +19301,24 @@
         </is>
       </c>
       <c r="G64" t="n">
+        <v>18</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>I will use the CER method to answer open-ended questions.</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
         <v>14</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>I will use the CER method to answer open-ended questions.</t>
-        </is>
-      </c>
-      <c r="I64" t="n">
-        <v>20</v>
       </c>
       <c r="J64" t="n">
         <v>20</v>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>I forgot some keywords. I will make flash cards.</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -19371,15 +19351,15 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>I will practise writing ten words a day.</t>
+          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
         <v>30</v>
@@ -19417,7 +19397,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -19425,16 +19405,12 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
         <v>30</v>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>I did not understand the question. I will read it twice next time.</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -19471,16 +19447,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>I will ask my teacher when I do not understand.</t>
+          <t>I will check my working step by step.</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J67" t="n">
         <v>25</v>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>I ran out of time. Next time I will skip difficult questions first.</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -19513,24 +19493,20 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>I will redo my wrong questions.</t>
+          <t>I will revise the keywords for each topic.</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
         <v>20</v>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>I ran out of time. Next time I will skip difficult questions first.</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -19571,16 +19547,12 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
         <v>30</v>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>I did better than my target because I practised a lot.</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
@@ -19613,24 +19585,20 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>I will read for 20 minutes every night.</t>
+          <t>I will learn five new words every week.</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
         <v>30</v>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>I did not reach my target because I was careless in the last section.</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -19663,7 +19631,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -19676,11 +19644,7 @@
       <c r="J71" t="n">
         <v>25</v>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>I ran out of time. Next time I will skip difficult questions first.</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -19713,15 +19677,15 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>I will revise the keywords for each topic.</t>
+          <t>I will redo my wrong questions.</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J72" t="n">
         <v>20</v>
@@ -19759,7 +19723,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -19767,12 +19731,16 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
         <v>30</v>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>I ran out of time. Next time I will skip difficult questions first.</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -19805,20 +19773,24 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>I will read for 20 minutes every night.</t>
+          <t>I will check my spelling before I hand in my work.</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
         <v>30</v>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>I did better than my target because I practised a lot.</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -19851,7 +19823,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -19859,12 +19831,16 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J75" t="n">
         <v>25</v>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>I did not understand the question. I will read it twice next time.</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -19897,11 +19873,11 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>I will use the CER method to answer open-ended questions.</t>
+          <t>I will revise the keywords for each topic.</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -19910,7 +19886,11 @@
       <c r="J76" t="n">
         <v>20</v>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>I did not reach my target because I was careless in the last section.</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -19943,7 +19923,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -19951,12 +19931,16 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
         <v>30</v>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>I did better than my target because I practised a lot.</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -19989,15 +19973,15 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>I will learn five new words every week.</t>
+          <t>I will read for 20 minutes every night.</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
         <v>30</v>
@@ -20035,15 +20019,15 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>I will check my working step by step.</t>
+          <t>I will ask my teacher when I do not understand.</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J79" t="n">
         <v>25</v>
@@ -20081,22 +20065,22 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>I will use the CER method to answer open-ended questions.</t>
+          <t>I will revise the keywords for each topic.</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
         <v>20</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>I did not understand the question. I will read it twice next time.</t>
+          <t>Reading every night helped me understand the questions.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -20131,7 +20115,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -20139,16 +20123,12 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
         <v>30</v>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Reading every night helped me understand the questions.</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -20185,11 +20165,11 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>I will read for 20 minutes every night.</t>
+          <t>I will check my spelling before I hand in my work.</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
         <v>30</v>
@@ -20227,15 +20207,15 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>I will check my working step by step.</t>
+          <t>I will ask my teacher when I do not understand.</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
         <v>25</v>
@@ -20273,15 +20253,15 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>I will use the CER method to answer open-ended questions.</t>
+          <t>I will redo my wrong questions.</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
         <v>20</v>
@@ -20319,15 +20299,15 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>I will read one Mother Tongue story every week.</t>
+          <t>I will practise writing ten words a day.</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
         <v>30</v>
@@ -20369,11 +20349,11 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>I will learn five new words every week.</t>
+          <t>I will read for 20 minutes every night.</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
         <v>30</v>
@@ -20411,7 +20391,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -20419,7 +20399,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J87" t="n">
         <v>25</v>
@@ -20457,15 +20437,15 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>I will use the CER method to answer open-ended questions.</t>
+          <t>I will redo my wrong questions.</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J88" t="n">
         <v>20</v>
@@ -20503,11 +20483,11 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>I will practise writing ten words a day.</t>
+          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -20549,7 +20529,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -20557,7 +20537,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J90" t="n">
         <v>30</v>
@@ -20595,7 +20575,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -20603,7 +20583,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J91" t="n">
         <v>25</v>
@@ -20641,15 +20621,15 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>I will redo my wrong questions.</t>
+          <t>I will use the CER method to answer open-ended questions.</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J92" t="n">
         <v>20</v>
@@ -20687,7 +20667,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -20737,11 +20717,11 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>I will learn five new words every week.</t>
+          <t>I will check my spelling before I hand in my work.</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J94" t="n">
         <v>30</v>
@@ -20779,7 +20759,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -20787,7 +20767,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J95" t="n">
         <v>25</v>
@@ -20833,7 +20813,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J96" t="n">
         <v>20</v>
@@ -20871,7 +20851,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -20879,7 +20859,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J97" t="n">
         <v>30</v>
@@ -20917,15 +20897,15 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>I will learn five new words every week.</t>
+          <t>I will check my spelling before I hand in my work.</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J98" t="n">
         <v>30</v>
@@ -20963,7 +20943,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -20971,7 +20951,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J99" t="n">
         <v>25</v>
@@ -21009,7 +20989,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -21055,15 +21035,15 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>I will read one Mother Tongue story every week.</t>
+          <t>I will practise writing ten words a day.</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J101" t="n">
         <v>30</v>
@@ -21101,15 +21081,15 @@
         </is>
       </c>
       <c r="G102" t="n">
+        <v>25</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>I will learn five new words every week.</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
         <v>24</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>I will learn five new words every week.</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>25</v>
       </c>
       <c r="J102" t="n">
         <v>30</v>
@@ -21147,15 +21127,15 @@
         </is>
       </c>
       <c r="G103" t="n">
+        <v>21</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>I will check my working step by step.</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
         <v>18</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>I will ask my teacher when I do not understand.</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>22</v>
       </c>
       <c r="J103" t="n">
         <v>25</v>
@@ -21193,15 +21173,15 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>I will revise the keywords for each topic.</t>
+          <t>I will use the CER method to answer open-ended questions.</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J104" t="n">
         <v>20</v>
@@ -21243,11 +21223,11 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>I will read one Mother Tongue story every week.</t>
+          <t>I will practise writing ten words a day.</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J105" t="n">
         <v>30</v>
@@ -21285,15 +21265,15 @@
         </is>
       </c>
       <c r="G106" t="n">
+        <v>23</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>I will check my spelling before I hand in my work.</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
         <v>22</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>I will check my spelling before I hand in my work.</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>23</v>
       </c>
       <c r="J106" t="n">
         <v>30</v>
@@ -21331,15 +21311,15 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>I will check my working step by step.</t>
+          <t>I will ask my teacher when I do not understand.</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J107" t="n">
         <v>25</v>
@@ -21377,7 +21357,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -21385,7 +21365,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J108" t="n">
         <v>20</v>
@@ -21423,15 +21403,15 @@
         </is>
       </c>
       <c r="G109" t="n">
+        <v>24</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>I will read one Mother Tongue story every week.</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
         <v>21</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>I will speak Mother Tongue at home for 15 minutes a day.</t>
-        </is>
-      </c>
-      <c r="I109" t="n">
-        <v>19</v>
       </c>
       <c r="J109" t="n">
         <v>30</v>
@@ -21471,7 +21451,7 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J110" t="n">
         <v>30</v>
@@ -21511,7 +21491,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J111" t="n">
         <v>25</v>
@@ -21551,7 +21531,7 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J112" t="n">
         <v>20</v>
@@ -21591,7 +21571,7 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J113" t="n">
         <v>30</v>
@@ -21631,7 +21611,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J114" t="n">
         <v>30</v>
@@ -21711,7 +21691,7 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J116" t="n">
         <v>20</v>
@@ -21751,7 +21731,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J117" t="n">
         <v>30</v>
@@ -21791,7 +21771,7 @@
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J118" t="n">
         <v>30</v>
@@ -21831,7 +21811,7 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J119" t="n">
         <v>25</v>
@@ -21871,7 +21851,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J120" t="n">
         <v>20</v>
@@ -21911,7 +21891,7 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J121" t="n">
         <v>30</v>
@@ -22011,7 +21991,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2027-03-13 13:34</t>
+          <t>2027-03-08 11:20</t>
         </is>
       </c>
     </row>
@@ -22051,7 +22031,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2027-03-12 12:05</t>
+          <t>2027-03-17 15:41</t>
         </is>
       </c>
     </row>
@@ -22091,7 +22071,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2027-03-15 16:41</t>
+          <t>2027-03-06 13:12</t>
         </is>
       </c>
     </row>
@@ -22127,7 +22107,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2027-03-09 12:58</t>
+          <t>2027-03-15 11:58</t>
         </is>
       </c>
     </row>
@@ -22167,7 +22147,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2027-03-10 15:34</t>
+          <t>2027-03-09 15:05</t>
         </is>
       </c>
     </row>
@@ -22207,7 +22187,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2027-03-06 09:12</t>
+          <t>2027-03-04 10:12</t>
         </is>
       </c>
     </row>
@@ -22323,7 +22303,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2027-03-20 10:05</t>
+          <t>2027-03-15 12:12</t>
         </is>
       </c>
     </row>
@@ -22373,7 +22353,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2027-03-18 14:12</t>
+          <t>2027-03-16 16:05</t>
         </is>
       </c>
     </row>
@@ -22423,7 +22403,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2027-03-17 15:20</t>
+          <t>2027-03-15 11:34</t>
         </is>
       </c>
     </row>
@@ -22473,7 +22453,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2027-03-20 13:05</t>
+          <t>2027-03-23 12:34</t>
         </is>
       </c>
     </row>
@@ -22523,7 +22503,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2027-03-15 15:20</t>
+          <t>2027-03-18 14:12</t>
         </is>
       </c>
     </row>
@@ -22573,7 +22553,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2027-03-19 16:34</t>
+          <t>2027-03-15 10:20</t>
         </is>
       </c>
     </row>
@@ -22605,7 +22585,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AK has set a clear reading goal. Suggest pairing it with a simple weekly log so progress is visible.</t>
+          <t>AP has set a clear learning goal. Suggest pairing it with a simple weekly log so progress is visible.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -22623,7 +22603,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2027-03-15 16:34</t>
+          <t>2027-03-22 14:41</t>
         </is>
       </c>
     </row>
@@ -22673,7 +22653,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2027-03-23 11:20</t>
+          <t>2027-03-19 13:41</t>
         </is>
       </c>
     </row>
@@ -22723,7 +22703,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2027-03-16 09:05</t>
+          <t>2027-03-24 15:58</t>
         </is>
       </c>
     </row>

--- a/seed/PHPPS_Portfolio_Data.xlsx
+++ b/seed/PHPPS_Portfolio_Data.xlsx
@@ -3473,7 +3473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I313"/>
+  <dimension ref="A1:I319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16262,6 +16262,252 @@
         </is>
       </c>
       <c r="I313" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>R00313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>S2027-0001</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Term 1 end</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>GR01</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>EV001</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>2027-03-08 11:20</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>R00314</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>S2027-0003</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Term 1 end</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>GR01</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>EV002</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>2027-03-17 15:41</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>R00315</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>S2027-0005</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Term 1 end</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>GR01</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>EV003</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr"/>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>2027-03-06 13:12</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>R00316</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>S2027-0010</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Term 1 end</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>GR01</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>EV004</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>2027-03-15 11:58</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>R00317</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>S2027-0014</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Term 1 end</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>GR01</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>EV005</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>2027-03-09 15:05</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Not needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>R00318</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>S2027-0020</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Term 1 end</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>GR01</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>EV006</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>2027-03-04 10:12</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
         <is>
           <t>Not needed</t>
         </is>
